--- a/OMs/Sardine/Tables/Various.xlsx
+++ b/OMs/Sardine/Tables/Various.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cassidy.peterson\Documents\Github\mahiMSE\docs\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ClimateTestMethods\OMs\Sardine\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC265F11-20FE-47B9-B0E5-B2FB1B58572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60B2F98-422B-40AF-8FCC-54CCCB92BCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4665" yWindow="900" windowWidth="15330" windowHeight="10770" tabRatio="827" firstSheet="13" activeTab="18" xr2:uid="{EE4263A2-8FC9-4695-B2B5-F7B8177F316B}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="827" xr2:uid="{EE4263A2-8FC9-4695-B2B5-F7B8177F316B}"/>
   </bookViews>
   <sheets>
     <sheet name="ToDo" sheetId="15" r:id="rId1"/>
@@ -48,15 +48,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="354">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -1066,33 +1063,6 @@
     <t>148 season-years + n age classes -1</t>
   </si>
   <si>
-    <t>Carry out peer-review of MSE framework</t>
-  </si>
-  <si>
-    <t>Are the current OMs, MPs and performance metrics sufficient to meet ToRs? Can the process now progress to formal MP testing and potentially adoption?</t>
-  </si>
-  <si>
-    <t>Alternative Indices of Abundance for MPs</t>
-  </si>
-  <si>
-    <t>Formalization of PR_tourn, MRIP, ENSO, Blue-Blob</t>
-  </si>
-  <si>
-    <t>Effort dynamics model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To model opportunity a model is needed to predict whether ACLs will be reached given available fishing characteristics. </t>
-  </si>
-  <si>
-    <t>Add landings by fleet to time series plots</t>
-  </si>
-  <si>
-    <t>Slick improvements</t>
-  </si>
-  <si>
-    <t>Make robustness slick or add to existing</t>
-  </si>
-  <si>
     <t xml:space="preserve">Based on FAO database. Assumed to have the same seasonal distribution as the USCom fleet. </t>
   </si>
   <si>
@@ -1133,6 +1103,18 @@
   </si>
   <si>
     <t>von Bertalanffy asymptotic length, L-infinity (male and female combined) (mm)</t>
+  </si>
+  <si>
+    <t>Current rec dev projections do not start from the last deviation (AC not carried forward)</t>
+  </si>
+  <si>
+    <t>Terminal deviation AC propagation for rec devs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possible 2 area </t>
+  </si>
+  <si>
+    <t>Extent to 2 area model with transitions</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1212,10 +1194,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1235,9 +1214,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1275,7 +1254,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1381,7 +1360,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1523,7 +1502,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1532,13 +1511,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A2B60A-BF4A-49C5-86BC-AAE256712F35}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.140625" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" customWidth="1"/>
+    <col min="1" max="1" width="53.36328125" customWidth="1"/>
+    <col min="2" max="2" width="39.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
@@ -1546,47 +1525,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>343</v>
-      </c>
-      <c r="B6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
     </row>
   </sheetData>
@@ -1597,13 +1552,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F87EF8B3-71A2-42AA-ACE0-0FF455C3A4FB}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>324</v>
       </c>
@@ -1611,7 +1566,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>316</v>
       </c>
@@ -1619,7 +1574,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>323</v>
       </c>
@@ -1627,7 +1582,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>322</v>
       </c>
@@ -1635,7 +1590,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>320</v>
       </c>
@@ -1651,29 +1606,29 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EAC486-A017-463D-8ADB-61E4EC63F3EE}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -1686,14 +1641,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081D8FC8-91C1-41A2-9BA3-CA12A708DF6A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" customWidth="1"/>
+    <col min="3" max="3" width="29.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1704,7 +1659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>153</v>
       </c>
@@ -1715,7 +1670,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1726,7 +1681,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -1737,7 +1692,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -1756,16 +1711,16 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A566BA38-7908-4D5C-90BF-A498D09C814B}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="42.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" customWidth="1"/>
+    <col min="3" max="3" width="26.54296875" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="6" max="6" width="42.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1785,12 +1740,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
         <v>65</v>
@@ -1802,10 +1757,10 @@
         <v>73</v>
       </c>
       <c r="F2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1825,7 +1780,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1845,7 +1800,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1865,7 +1820,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1885,7 +1840,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1901,11 +1856,11 @@
       <c r="E7" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1921,11 +1876,11 @@
       <c r="E8" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1941,8 +1896,8 @@
       <c r="E9" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>346</v>
+      <c r="F9" t="s">
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -1953,13 +1908,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9B310C-599A-4BAB-B51A-E74D7F51AC0B}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="53.5703125" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="53.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -1967,7 +1922,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -1975,7 +1930,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -1983,15 +1938,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -1999,7 +1954,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -2007,7 +1962,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>330</v>
       </c>
@@ -2023,13 +1978,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5657926F-43CB-455A-AC6E-4954BADA8C82}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -2040,7 +1995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>154</v>
       </c>
@@ -2051,7 +2006,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>156</v>
       </c>
@@ -2062,7 +2017,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -2073,7 +2028,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -2084,7 +2039,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>157</v>
       </c>
@@ -2092,7 +2047,7 @@
         <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -2103,14 +2058,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47864489-C592-46C6-B98F-008C606ED044}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
@@ -2124,7 +2079,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -2138,7 +2093,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>152</v>
       </c>
@@ -2152,7 +2107,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -2166,7 +2121,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>152</v>
       </c>
@@ -2180,7 +2135,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>88</v>
       </c>
@@ -2194,7 +2149,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -2208,7 +2163,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -2222,7 +2177,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>152</v>
       </c>
@@ -2236,7 +2191,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>152</v>
       </c>
@@ -2258,13 +2213,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26CB1A4-32CC-40D1-B203-9F91BD896760}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="41.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -2272,7 +2227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -2280,7 +2235,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -2288,7 +2243,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -2296,7 +2251,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -2312,13 +2267,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97162EB3-8C36-45A6-A7F5-E11890F2B3BC}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="105.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="105.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>109</v>
       </c>
@@ -2326,7 +2281,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>110</v>
       </c>
@@ -2334,7 +2289,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>112</v>
       </c>
@@ -2342,7 +2297,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>114</v>
       </c>
@@ -2350,7 +2305,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -2358,7 +2313,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>118</v>
       </c>
@@ -2366,7 +2321,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -2374,7 +2329,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>122</v>
       </c>
@@ -2382,7 +2337,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -2398,16 +2353,16 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06522138-93B3-4409-93D1-7697414686F5}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="75.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" customWidth="1"/>
-    <col min="5" max="5" width="42.85546875" customWidth="1"/>
+    <col min="1" max="1" width="75.26953125" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" customWidth="1"/>
+    <col min="5" max="5" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>251</v>
       </c>
@@ -2424,7 +2379,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>247</v>
       </c>
@@ -2441,9 +2396,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B3">
         <v>1289</v>
@@ -2458,12 +2413,12 @@
         <v>242</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>246</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C4" t="s">
         <v>233</v>
@@ -2475,7 +2430,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>245</v>
       </c>
@@ -2492,7 +2447,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>248</v>
       </c>
@@ -2509,7 +2464,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>243</v>
       </c>
@@ -2526,7 +2481,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>244</v>
       </c>
@@ -2543,7 +2498,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>232</v>
       </c>
@@ -2560,7 +2515,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>237</v>
       </c>
@@ -2571,13 +2526,13 @@
         <v>239</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="E10" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>236</v>
       </c>
@@ -2594,7 +2549,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -2604,42 +2559,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9680D609-91F9-4C15-AAA9-F73651BACC8D}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -2652,13 +2607,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70822580-D34B-4110-AF41-EF4D8F8C8CF2}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
     <col min="2" max="2" width="87" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>85</v>
       </c>
@@ -2666,7 +2621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>126</v>
       </c>
@@ -2674,7 +2629,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>128</v>
       </c>
@@ -2682,7 +2637,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>130</v>
       </c>
@@ -2690,7 +2645,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>132</v>
       </c>
@@ -2698,7 +2653,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>134</v>
       </c>
@@ -2706,7 +2661,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="65.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>136</v>
       </c>
@@ -2714,7 +2669,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>138</v>
       </c>
@@ -2722,7 +2677,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>140</v>
       </c>
@@ -2730,7 +2685,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>142</v>
       </c>
@@ -2738,7 +2693,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>144</v>
       </c>
@@ -2746,7 +2701,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>146</v>
       </c>
@@ -2754,7 +2709,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>148</v>
       </c>
@@ -2762,7 +2717,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="39.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>150</v>
       </c>
@@ -2778,60 +2733,60 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E084CD2-D73D-4BCF-9E66-EB835B19C48C}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2843,12 +2798,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D0E3CA-ADCA-4689-A286-6277FDD311C5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="22.5703125" customWidth="1"/>
+    <col min="1" max="3" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2859,7 +2814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2870,7 +2825,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2881,7 +2836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -2892,7 +2847,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2903,7 +2858,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2922,9 +2877,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5914CF4D-5333-407A-A26F-9917FF960A73}">
   <dimension ref="A1:F33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -2944,7 +2899,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>183</v>
       </c>
@@ -2964,7 +2919,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>184</v>
       </c>
@@ -2984,7 +2939,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>185</v>
       </c>
@@ -3004,7 +2959,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>186</v>
       </c>
@@ -3024,7 +2979,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -3044,7 +2999,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>188</v>
       </c>
@@ -3064,7 +3019,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>189</v>
       </c>
@@ -3084,7 +3039,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>190</v>
       </c>
@@ -3104,7 +3059,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>191</v>
       </c>
@@ -3124,7 +3079,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>192</v>
       </c>
@@ -3144,7 +3099,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>193</v>
       </c>
@@ -3164,7 +3119,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>194</v>
       </c>
@@ -3184,7 +3139,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>195</v>
       </c>
@@ -3204,7 +3159,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>196</v>
       </c>
@@ -3224,7 +3179,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>197</v>
       </c>
@@ -3244,7 +3199,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>198</v>
       </c>
@@ -3264,7 +3219,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>199</v>
       </c>
@@ -3284,7 +3239,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>200</v>
       </c>
@@ -3304,7 +3259,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>201</v>
       </c>
@@ -3324,7 +3279,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>202</v>
       </c>
@@ -3344,7 +3299,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>203</v>
       </c>
@@ -3364,7 +3319,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>204</v>
       </c>
@@ -3384,7 +3339,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>205</v>
       </c>
@@ -3404,7 +3359,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>206</v>
       </c>
@@ -3424,7 +3379,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>207</v>
       </c>
@@ -3444,7 +3399,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>208</v>
       </c>
@@ -3464,7 +3419,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>209</v>
       </c>
@@ -3484,7 +3439,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>210</v>
       </c>
@@ -3504,7 +3459,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>211</v>
       </c>
@@ -3524,7 +3479,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>212</v>
       </c>
@@ -3544,7 +3499,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>213</v>
       </c>
@@ -3564,7 +3519,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>214</v>
       </c>
@@ -3592,14 +3547,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D760A6-0824-4E71-80B5-1B4ED9B6FA8E}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" customWidth="1"/>
+    <col min="3" max="3" width="37.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>257</v>
       </c>
@@ -3610,7 +3565,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>303</v>
       </c>
@@ -3621,7 +3576,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>259</v>
       </c>
@@ -3632,7 +3587,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>262</v>
       </c>
@@ -3643,7 +3598,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>231</v>
       </c>
@@ -3654,7 +3609,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>231</v>
       </c>
@@ -3673,13 +3628,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA40A8BC-C366-49A3-87C6-4B9DEB0D3E33}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.140625" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="51.1796875" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>277</v>
       </c>
@@ -3687,7 +3642,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>268</v>
       </c>
@@ -3695,7 +3650,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>270</v>
       </c>
@@ -3703,7 +3658,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>272</v>
       </c>
@@ -3711,7 +3666,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>297</v>
       </c>
@@ -3719,7 +3674,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>275</v>
       </c>
@@ -3727,7 +3682,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>295</v>
       </c>
@@ -3735,7 +3690,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>292</v>
       </c>
@@ -3743,7 +3698,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>291</v>
       </c>
@@ -3751,7 +3706,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>298</v>
       </c>
@@ -3759,7 +3714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>300</v>
       </c>
@@ -3767,7 +3722,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>301</v>
       </c>
@@ -3783,15 +3738,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDCC00A-806A-4ED8-9F4D-5FFC556579AD}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="76.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="76.26953125" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>251</v>
       </c>
@@ -3805,7 +3760,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>279</v>
       </c>
@@ -3819,7 +3774,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>280</v>
       </c>
@@ -3833,7 +3788,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>281</v>
       </c>
@@ -3847,7 +3802,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>282</v>
       </c>
@@ -3861,7 +3816,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>283</v>
       </c>
@@ -3875,7 +3830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>231</v>
       </c>
@@ -3898,13 +3853,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12DE8661-58F7-4A4D-9F7C-724104DE0CE4}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="13.140625" customWidth="1"/>
-    <col min="3" max="3" width="59.140625" customWidth="1"/>
+    <col min="1" max="2" width="13.1796875" customWidth="1"/>
+    <col min="3" max="3" width="59.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -3915,7 +3870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>215</v>
       </c>
@@ -3926,7 +3881,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>307</v>
       </c>
@@ -3937,7 +3892,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>216</v>
       </c>
@@ -3948,7 +3903,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>217</v>
       </c>
@@ -3959,7 +3914,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>218</v>
       </c>
@@ -3970,7 +3925,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>219</v>
       </c>
@@ -3981,7 +3936,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>220</v>
       </c>
@@ -3992,7 +3947,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>221</v>
       </c>
@@ -4003,7 +3958,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>222</v>
       </c>
@@ -4014,7 +3969,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>223</v>
       </c>
@@ -4025,7 +3980,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>224</v>
       </c>
@@ -4036,7 +3991,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>225</v>
       </c>
@@ -4047,7 +4002,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>226</v>
       </c>
@@ -4058,7 +4013,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>227</v>
       </c>
@@ -4069,7 +4024,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>304</v>
       </c>
@@ -4080,7 +4035,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>305</v>
       </c>

--- a/OMs/Sardine/Tables/Various.xlsx
+++ b/OMs/Sardine/Tables/Various.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ClimateTestMethods\OMs\Sardine\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CA4051-0A4B-4E40-82AD-9DE0D2C9009C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381619B5-EB1B-45BE-B6A7-C7C38628511E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="827" xr2:uid="{EE4263A2-8FC9-4695-B2B5-F7B8177F316B}"/>
   </bookViews>
@@ -42,16 +42,16 @@
     <t>Limitation / new feature / bug</t>
   </si>
   <si>
-    <t>Current rec dev projections do not start from the last deviation (AC not carried forward)</t>
-  </si>
-  <si>
-    <t>Terminal deviation AC propagation for rec devs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Possible 2 area </t>
   </si>
   <si>
     <t>Extent to 2 area model with transitions</t>
+  </si>
+  <si>
+    <t>Update SR estimations to use SSB</t>
+  </si>
+  <si>
+    <t>Currentlythe estimates of SSB from the assessment are not available</t>
   </si>
 </sst>
 </file>
@@ -423,11 +423,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A2B60A-BF4A-49C5-86BC-AAE256712F35}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.36328125" customWidth="1"/>
-    <col min="2" max="2" width="39.7265625" customWidth="1"/>
+    <col min="1" max="1" width="41.453125" customWidth="1"/>
+    <col min="2" max="2" width="79.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -440,22 +440,22 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B12" s="2"/>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
